--- a/docs/downloads/04/tbl_cm_educ_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -438,32 +438,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>9.800000000000001</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>1.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="7">
@@ -474,14 +474,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D7">
-        <v>10.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="8">
@@ -492,14 +492,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C8">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D8">
-        <v>53.7</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="9">
@@ -510,32 +510,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C9">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D9">
-        <v>28.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D10">
-        <v>7.3</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="11">
@@ -546,14 +546,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="D11">
-        <v>21.9</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="12">
@@ -564,14 +564,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C12">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D12">
-        <v>58.4</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="13">
@@ -582,32 +582,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>14.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D14">
-        <v>5.1</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="15">
@@ -618,14 +618,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C15">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="D15">
-        <v>12.9</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="16">
@@ -636,14 +636,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C16">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D16">
-        <v>46.6</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="17">
@@ -654,32 +654,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C17">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>33.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="D18">
-        <v>6.9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -690,14 +690,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C19">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="D19">
-        <v>15.4</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="20">
@@ -708,14 +708,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C20">
-        <v>269</v>
+        <v>130</v>
       </c>
       <c r="D20">
-        <v>51.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -726,50 +726,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C21">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="D21">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>38</v>
-      </c>
-      <c r="D22">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>0.4</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_educ_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,12 +387,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="C2">
-        <v>22</v>
-      </c>
-      <c r="D2">
-        <v>15.4</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -402,14 +396,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C3">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>48.3</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="4">
@@ -420,14 +414,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D4">
-        <v>25.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="5">
@@ -438,32 +432,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D5">
-        <v>11.2</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="7">
@@ -474,14 +468,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C7">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>53.7</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="8">
@@ -492,14 +486,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C8">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D8">
-        <v>28.5</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="9">
@@ -510,32 +504,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D9">
-        <v>7.3</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>20.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="11">
@@ -546,14 +540,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C11">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>58.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
@@ -564,14 +558,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D12">
-        <v>14.6</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="13">
@@ -582,50 +576,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="D13">
-        <v>6.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D14">
-        <v>12.9</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C15">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D15">
-        <v>46.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="16">
@@ -636,14 +630,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C16">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D16">
-        <v>33.6</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="17">
@@ -654,50 +648,50 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D17">
-        <v>6.9</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C18">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="D18">
-        <v>15</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C19">
-        <v>269</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>51.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="20">
@@ -708,14 +702,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C20">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21">
@@ -726,13 +720,67 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>72</v>
+      </c>
+      <c r="D21">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>269</v>
+      </c>
+      <c r="D22">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>130</v>
+      </c>
+      <c r="D23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
-      <c r="C21">
+      <c r="C24">
         <v>42</v>
       </c>
-      <c r="D21">
+      <c r="D24">
         <v>8.1</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_cm_educ_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
